--- a/Design/Excel/GameHot/Datas/__tables__.xlsx
+++ b/Design/Excel/GameHot/Datas/__tables__.xlsx
@@ -1053,603 +1053,603 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>value_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>read_schema_from_file</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>output</t>
         </is>
       </c>
     </row>
     <row r="2" customFormat="1" s="1">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>全名(包含模块和名字)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>记录类名</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>从excel读取定义</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>文件列表</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>表id字段</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>模式</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>注释</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>输出文件名</t>
         </is>
       </c>
     </row>
     <row r="3" customFormat="1" s="1">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>可以多个，以逗号','分隔</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>取值one|map|list，为空自动为map</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
         </is>
       </c>
     </row>
     <row r="4" customFormat="1" s="3">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>DTUIForm</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>DRUIForm</t>
         </is>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Game/UI.xlsx</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>gc,ge</t>
         </is>
       </c>
     </row>
     <row r="5" customFormat="1" s="3">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>DTEntity</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>DREntity</t>
         </is>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Game/Entity.xlsx</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>gc,ge</t>
         </is>
       </c>
     </row>
     <row r="6" customFormat="1" s="3">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>DTScene</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>DRScene</t>
         </is>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Game/Scene.xlsx</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>gc,ge</t>
         </is>
       </c>
     </row>
     <row r="7" customFormat="1" s="3">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>DTSound</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>DRSound</t>
         </is>
       </c>
-      <c r="D7" t="b">
+      <c r="D7" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Game/Sound@Sound.xlsx</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>gc,ge</t>
         </is>
       </c>
     </row>
     <row r="8" customFormat="1" s="3">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>DTUISound</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>DRUISound</t>
         </is>
       </c>
-      <c r="D8" t="b">
+      <c r="D8" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Game/UISound@Sound.xlsx</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>gc,ge</t>
         </is>
       </c>
     </row>
     <row r="9" customFormat="1" s="3">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>DTMusic</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>DRMusic</t>
         </is>
       </c>
-      <c r="D9" t="b">
+      <c r="D9" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Game/Music@Sound.xlsx</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>gc,ge</t>
         </is>
       </c>
     </row>
     <row r="10" customFormat="1" s="3">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>DTUIEntity</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>DRUIEntity</t>
         </is>
       </c>
-      <c r="D10" t="b">
+      <c r="D10" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Game/UIEntity.xlsx</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>gc,ge</t>
         </is>
       </c>
     </row>
     <row r="11" s="8">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>DTOneConfig</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>DROneConfig</t>
         </is>
       </c>
-      <c r="D11" t="b">
+      <c r="D11" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>OneConfig.xlsx</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>c,e</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>DTAircraft</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>DRAircraft</t>
         </is>
       </c>
-      <c r="D12" t="b">
+      <c r="D12" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Aircraft.xlsx</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>c,e</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>DTArmor</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>DRArmor</t>
         </is>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Armor.xlsx</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>c,e</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>DTAsteroid</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>DRAsteroid</t>
         </is>
       </c>
-      <c r="D14" t="b">
+      <c r="D14" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Asteroid.xlsx</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>c,e</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>DTThruster</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>DRThruster</t>
         </is>
       </c>
-      <c r="D15" t="b">
+      <c r="D15" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Thruster.xlsx</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>c,e</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>DTWeapon</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>DRWeapon</t>
         </is>
       </c>
-      <c r="D16" t="b">
+      <c r="D16" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Weapon.xlsx</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>c,e</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>DTBuqiGlobal</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>DRBuqiGlobal</t>
         </is>
       </c>
-      <c r="D17" t="b">
+      <c r="D17" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Buqi/BuqiGlobal.xlsx</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>c,e</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Buqi global battle rules</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>DTBuqiItem</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>DRBuqiItem</t>
         </is>
       </c>
-      <c r="D18" t="b">
+      <c r="D18" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Buqi/BuqiItem.xlsx</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>c,e</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Buqi Step 3 nine items</t>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Buqi expanded effect items</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>DTBuqiRefinement</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>DRBuqiRefinement</t>
         </is>
       </c>
-      <c r="D19" t="b">
+      <c r="D19" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Buqi/BuqiRefinement.xlsx</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>c,e</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Buqi Step 3 three refinements</t>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Buqi six refinements</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>DTBuqiEcho</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>DRBuqiEcho</t>
         </is>
       </c>
-      <c r="D20" t="b">
+      <c r="D20" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>Buqi/BuqiEcho.xlsx</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>c,e</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Buqi Step 3 six echoes</t>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Buqi expanded build echoes</t>
         </is>
       </c>
     </row>
